--- a/data.xlsx
+++ b/data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>hệ nội đan</t>
   </si>
@@ -44,6 +44,9 @@
     <t>tác dụng</t>
   </si>
   <si>
+    <t>dohiem</t>
+  </si>
+  <si>
     <t xml:space="preserve">thông dụng cường hóa - toàn đội </t>
   </si>
   <si>
@@ -53,12 +56,18 @@
     <t>tự động nhảy lên khi rơi xuống nước, hiệu lực 2 lần</t>
   </si>
   <si>
+    <t>do</t>
+  </si>
+  <si>
     <t>truy kích nội đan</t>
   </si>
   <si>
     <t>số lần kĩ năng khi suy yếu +1</t>
   </si>
   <si>
+    <t>vang</t>
+  </si>
+  <si>
     <t>băng tương nội đan</t>
   </si>
   <si>
@@ -77,6 +86,9 @@
     <t>trong 8s sau khi hồi sinh, giảm st tăng 30%</t>
   </si>
   <si>
+    <t>tim</t>
+  </si>
+  <si>
     <t>đầu trận toàn đội bị đóng băng và không thể nhận st trong 5s</t>
   </si>
   <si>
@@ -114,6 +126,9 @@
   </si>
   <si>
     <t>công kích +6%</t>
+  </si>
+  <si>
+    <t>xanh</t>
   </si>
   <si>
     <t>tăng thương nội đan</t>
@@ -2482,17 +2497,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="11.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="20.447619047619" customWidth="1"/>
     <col min="4" max="4" width="22.2190476190476" customWidth="1"/>
-    <col min="5" max="5" width="52.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="116.285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2508,325 +2523,409 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="51" customHeight="1" spans="1:5">
+    <row r="2" ht="51" customHeight="1" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:5">
+    <row r="3" ht="60" customHeight="1" spans="1:6">
       <c r="B3">
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" spans="1:5">
+    <row r="4" ht="54" customHeight="1" spans="1:6">
       <c r="B4">
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" ht="64" customHeight="1" spans="1:5">
+    <row r="5" ht="64" customHeight="1" spans="1:6">
       <c r="B5">
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="6" ht="59" customHeight="1" spans="1:5">
+    <row r="6" ht="59" customHeight="1" spans="1:6">
       <c r="B6">
         <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="7" ht="62" customHeight="1" spans="1:5">
+    <row r="7" ht="62" customHeight="1" spans="1:6">
       <c r="B7">
         <v>6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1" spans="1:5">
+    <row r="8" ht="65" customHeight="1" spans="1:6">
       <c r="B8">
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1" spans="1:5">
+    <row r="9" ht="62" customHeight="1" spans="1:6">
       <c r="B9">
         <v>8</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:5">
+    <row r="10" ht="60" customHeight="1" spans="1:6">
       <c r="B10">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="11" ht="61" customHeight="1" spans="1:5">
+    <row r="11" ht="61" customHeight="1" spans="1:6">
       <c r="B11">
         <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="12" ht="57" customHeight="1" spans="1:5">
+    <row r="12" ht="57" customHeight="1" spans="1:6">
       <c r="B12">
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="13" ht="57" customHeight="1" spans="1:5">
+    <row r="13" ht="57" customHeight="1" spans="1:6">
       <c r="B13">
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="14" ht="61" customHeight="1" spans="1:5">
+    <row r="14" ht="61" customHeight="1" spans="1:6">
       <c r="B14">
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:5">
+    <row r="15" ht="60" customHeight="1" spans="1:6">
       <c r="B15">
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" spans="1:5">
+    <row r="16" ht="60" customHeight="1" spans="1:6">
       <c r="B16">
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
         <v>33</v>
       </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="17" ht="59" customHeight="1" spans="1:5">
+    <row r="17" ht="59" customHeight="1" spans="1:6">
       <c r="B17">
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="18" ht="61" customHeight="1" spans="1:5">
+    <row r="18" ht="61" customHeight="1" spans="1:6">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1" spans="1:5">
+    <row r="19" ht="58" customHeight="1" spans="1:6">
       <c r="B19">
         <v>2</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1" spans="1:5">
+    <row r="20" ht="58" customHeight="1" spans="1:6">
       <c r="B20">
         <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1" spans="1:5">
+    <row r="21" ht="58" customHeight="1" spans="1:6">
       <c r="B21">
         <v>4</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="22" ht="63" customHeight="1" spans="1:5">
+    <row r="22" ht="63" customHeight="1" spans="1:6">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1" spans="1:5">
+    <row r="23" ht="58" customHeight="1" spans="1:6">
       <c r="B23">
         <v>2</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1" spans="1:5">
+    <row r="24" ht="58" customHeight="1" spans="1:6">
       <c r="B24">
         <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="25" ht="61" customHeight="1" spans="1:5">
+    <row r="25" ht="61" customHeight="1" spans="1:6">
       <c r="B25">
         <v>4</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="26" ht="59" customHeight="1" spans="1:5">
+    <row r="26" ht="59" customHeight="1" spans="1:6">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="27" ht="62" customHeight="1" spans="1:5">
+    <row r="27" ht="62" customHeight="1" spans="1:6">
       <c r="B27">
         <v>2</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>60</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="28" ht="63" customHeight="1" spans="1:5">
+    <row r="28" ht="63" customHeight="1" spans="1:6">
       <c r="B28">
         <v>3</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="29" ht="63" customHeight="1" spans="1:5">
+    <row r="29" ht="63" customHeight="1" spans="1:6">
       <c r="B29">
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
